--- a/data/trans_bre/P45C_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P45C_R2-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 8,79</t>
+          <t>-2,44; 8,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 4,92</t>
+          <t>-7,33; 4,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 6,16</t>
+          <t>-5,61; 6,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 9,77</t>
+          <t>-9,15; 9,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 41,01</t>
+          <t>-8,98; 41,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,22; 17,69</t>
+          <t>-21,26; 16,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 28,89</t>
+          <t>-20,52; 29,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-33,55; 59,16</t>
+          <t>-34,16; 62,34</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 1,36</t>
+          <t>-6,83; 1,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,08; -5,74</t>
+          <t>-14,77; -5,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 8,3</t>
+          <t>-1,47; 8,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,71; -1,5</t>
+          <t>-18,17; -1,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,14; 7,52</t>
+          <t>-29,07; 9,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-55,11; -24,55</t>
+          <t>-54,22; -24,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 51,32</t>
+          <t>-6,95; 48,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,93; -8,75</t>
+          <t>-60,71; -8,2</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 0,46</t>
+          <t>-6,99; 0,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 2,94</t>
+          <t>-5,76; 2,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 4,99</t>
+          <t>-2,36; 4,93</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,54; -0,32</t>
+          <t>-9,65; -0,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-40,41; 4,73</t>
+          <t>-41,89; 3,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,34; 21,31</t>
+          <t>-31,42; 18,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 49,1</t>
+          <t>-16,36; 45,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-40,13; -1,87</t>
+          <t>-41,04; -6,03</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,5; -2,22</t>
+          <t>-10,75; -2,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,22; -1,0</t>
+          <t>-9,6; -0,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 2,53</t>
+          <t>-4,47; 3,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 9,83</t>
+          <t>-3,18; 10,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,79; -15,58</t>
+          <t>-57,32; -14,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-48,55; -5,61</t>
+          <t>-49,29; -4,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,28; 24,74</t>
+          <t>-31,26; 34,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 206,4</t>
+          <t>-20,04; 181,01</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 1,1</t>
+          <t>-6,66; 1,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 3,47</t>
+          <t>-4,78; 2,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 4,22</t>
+          <t>-4,11; 4,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 1,7</t>
+          <t>-5,14; 1,51</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-56,51; 16,31</t>
+          <t>-57,43; 17,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,74; 43,16</t>
+          <t>-39,39; 36,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 50,31</t>
+          <t>-32,22; 49,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-32,64; 15,57</t>
+          <t>-33,6; 13,83</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 2,22</t>
+          <t>-4,62; 2,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 2,71</t>
+          <t>-5,6; 2,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 5,71</t>
+          <t>-2,76; 5,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,69; -1,04</t>
+          <t>-9,24; -1,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-63,27; 69,3</t>
+          <t>-64,97; 61,87</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-57,41; 52,84</t>
+          <t>-58,3; 51,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,17; 139,25</t>
+          <t>-33,98; 127,44</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-81,04; -13,75</t>
+          <t>-82,06; -12,93</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,32; -1,18</t>
+          <t>-8,27; -1,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 4,63</t>
+          <t>-1,49; 4,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 2,16</t>
+          <t>-4,4; 2,02</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,5; -0,16</t>
+          <t>-5,74; -0,05</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-94,31; -17,65</t>
+          <t>-93,7; -6,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 323,85</t>
+          <t>-38,51; 337,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-69,53; 75,97</t>
+          <t>-66,52; 99,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-59,25; -2,34</t>
+          <t>-57,53; 1,49</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,02; -1,54</t>
+          <t>-5,02; -1,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,01; -2,46</t>
+          <t>-5,87; -2,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1,78</t>
+          <t>-1,78; 1,59</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,87; 0,41</t>
+          <t>-5,7; 0,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,3; -10,23</t>
+          <t>-30,18; -11,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,46; -14,79</t>
+          <t>-31,51; -14,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 13,7</t>
+          <t>-12,48; 12,44</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,56; 1,39</t>
+          <t>-34,65; 2,31</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P45C_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P45C_R2-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,17</t>
+          <t>-0,43</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>-2,01%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 8,95</t>
+          <t>-1,84; 8,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 4,84</t>
+          <t>-7,7; 4,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 6,16</t>
+          <t>-5,32; 6,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 9,66</t>
+          <t>-10,12; 7,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 41,69</t>
+          <t>-6,89; 40,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-21,26; 16,87</t>
+          <t>-22,47; 17,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-20,52; 29,06</t>
+          <t>-20,4; 31,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-34,16; 62,34</t>
+          <t>-37,97; 45,18</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-8,38</t>
+          <t>-7,26</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-32,27%</t>
+          <t>-27,18%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 1,77</t>
+          <t>-7,05; 1,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,77; -5,71</t>
+          <t>-14,63; -5,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 8,37</t>
+          <t>-1,38; 8,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,17; -1,84</t>
+          <t>-13,41; -0,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,07; 9,58</t>
+          <t>-29,71; 10,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,22; -24,77</t>
+          <t>-53,77; -25,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 48,86</t>
+          <t>-6,2; 50,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,71; -8,2</t>
+          <t>-44,46; -0,64</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-5,18</t>
+          <t>-5,08</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-24,79%</t>
+          <t>-24,52%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 0,43</t>
+          <t>-7,04; 0,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 2,63</t>
+          <t>-5,09; 2,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 4,93</t>
+          <t>-2,85; 4,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,65; -0,95</t>
+          <t>-9,46; -0,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-41,89; 3,62</t>
+          <t>-41,05; 4,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,42; 18,3</t>
+          <t>-27,46; 19,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,36; 45,99</t>
+          <t>-19,89; 44,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-41,04; -6,03</t>
+          <t>-40,52; -3,63</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,21</t>
+          <t>-1,8</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>-11,42%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,75; -2,09</t>
+          <t>-10,75; -1,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,6; -0,73</t>
+          <t>-9,52; -1,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 3,1</t>
+          <t>-4,67; 2,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 10,15</t>
+          <t>-5,39; 1,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-57,32; -14,11</t>
+          <t>-57,23; -14,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,29; -4,6</t>
+          <t>-50,12; -7,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,26; 34,48</t>
+          <t>-33,8; 23,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 181,01</t>
+          <t>-30,29; 10,83</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,68</t>
+          <t>-1,52</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-12,64%</t>
+          <t>-11,4%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 1,28</t>
+          <t>-6,89; 1,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 2,95</t>
+          <t>-4,97; 3,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 4,48</t>
+          <t>-4,29; 4,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 1,51</t>
+          <t>-4,96; 1,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-57,43; 17,75</t>
+          <t>-56,08; 14,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,39; 36,52</t>
+          <t>-38,95; 40,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-32,22; 49,96</t>
+          <t>-33,87; 46,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-33,6; 13,83</t>
+          <t>-32,36; 13,17</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-4,49</t>
+          <t>-3,01</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-49,33%</t>
+          <t>-30,33%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,62; 2,21</t>
+          <t>-4,82; 2,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 2,26</t>
+          <t>-6,19; 2,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 5,53</t>
+          <t>-2,36; 5,32</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,24; -1,23</t>
+          <t>-6,23; -0,15</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-64,97; 61,87</t>
+          <t>-62,86; 71,69</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-58,3; 51,12</t>
+          <t>-62,0; 49,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-33,98; 127,44</t>
+          <t>-30,38; 122,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-82,06; -12,93</t>
+          <t>-51,83; -0,51</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-2,76</t>
+          <t>-2,96</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-36,97%</t>
+          <t>-38,69%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,27; -1,42</t>
+          <t>-8,35; -1,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 4,65</t>
+          <t>-1,8; 4,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 2,02</t>
+          <t>-4,44; 2,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,74; -0,05</t>
+          <t>-5,83; -0,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-93,7; -6,58</t>
+          <t>-94,27; -15,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-38,51; 337,07</t>
+          <t>-39,07; 302,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-66,52; 99,13</t>
+          <t>-65,44; 88,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-57,53; 1,49</t>
+          <t>-60,89; -3,63</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-3,1</t>
+          <t>-3,64</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-20,11%</t>
+          <t>-21,43%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,02; -1,66</t>
+          <t>-5,0; -1,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-5,87; -2,35</t>
+          <t>-5,68; -2,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,59</t>
+          <t>-1,63; 1,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 0,54</t>
+          <t>-5,42; -1,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,18; -11,33</t>
+          <t>-30,11; -11,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-31,51; -14,13</t>
+          <t>-30,73; -14,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-12,48; 12,44</t>
+          <t>-11,5; 13,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,65; 2,31</t>
+          <t>-29,8; -11,9</t>
         </is>
       </c>
     </row>
